--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -11,7 +11,7 @@
     <sheet name="注記" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'商品一覧'!$A$1:$P$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'商品一覧'!$A$1:$P$355</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P343"/>
+  <dimension ref="A1:P355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -578,14 +578,14 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3698</v>
+        <v>3673</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -609,17 +609,17 @@
         <v>3243</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1621718</v>
+        <v>1621555</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -670,20 +670,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>99137</v>
+        <v>99127</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>25947</v>
+        <v>25945</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25947</v>
+        <v>25945</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>24326</v>
+        <v>24323</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>24326</v>
+        <v>24323</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>24326</v>
+        <v>24323</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>24326</v>
+        <v>24323</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>48652</v>
+        <v>48647</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>43786</v>
+        <v>43782</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43786</v>
+        <v>43782</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>43786</v>
+        <v>43782</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>74249</v>
+        <v>74241</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>87573</v>
+        <v>87564</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -926,20 +926,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>145955</v>
+        <v>145940</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>145955</v>
+        <v>145940</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>259475</v>
+        <v>259449</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -980,20 +980,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>364887</v>
+        <v>364850</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>364887</v>
+        <v>364850</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>729773</v>
+        <v>729700</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1012,18 +1012,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6597</v>
+        <v>5778</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>37</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6411</v>
+        <v>6396</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1044,20 +1044,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6681</v>
+        <v>6504</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1621718</v>
+        <v>1621555</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8919</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1076,18 +1076,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8639</v>
+        <v>8589</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>52</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9114</v>
+        <v>9105</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1108,20 +1108,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8728</v>
+        <v>8722</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>154021</v>
+        <v>154006</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17839</v>
+        <v>17837</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1140,18 +1140,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14271</v>
+        <v>14270</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
         <v>26</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14781</v>
+        <v>14779</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1172,20 +1172,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>14957</v>
+        <v>14270</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>43542</v>
+        <v>43537</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>35678</v>
+        <v>35674</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1226,20 +1226,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>24454</v>
+        <v>24528</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>40543</v>
+        <v>40539</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22704</v>
+        <v>22702</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1280,20 +1280,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>96361</v>
+        <v>96351</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>96361</v>
+        <v>96351</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22704</v>
+        <v>22702</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1334,20 +1334,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1621718</v>
+        <v>1621555</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1621718</v>
+        <v>1621555</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1388,20 +1388,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>35154</v>
+        <v>35150</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>65697</v>
+        <v>65691</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5514</v>
+        <v>5513</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1442,20 +1442,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>14672</v>
+        <v>14716</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>65697</v>
+        <v>65691</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5514</v>
+        <v>5513</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
         <v>811</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1621718</v>
+        <v>1621555</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1622</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
         <v>1622</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>233542</v>
+        <v>233519</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3243</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1607,17 +1607,17 @@
         <v>3243</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>275692</v>
+        <v>275664</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>5838</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22704</v>
+        <v>22702</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11676</v>
+        <v>11675</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1712,20 +1712,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11352</v>
+        <v>11351</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>37900</v>
+        <v>37896</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22704</v>
+        <v>22702</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1766,20 +1766,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21893</v>
+        <v>21891</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>143149</v>
+        <v>143135</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>43786</v>
+        <v>43782</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>40543</v>
+        <v>40539</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>40543</v>
+        <v>40539</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1830,20 +1830,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>40543</v>
+        <v>40539</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>329754</v>
+        <v>329721</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>81086</v>
+        <v>81078</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
         <v>2523</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>324</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1959,20 +1959,20 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1545</v>
+        <v>1455</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2016,17 +2016,17 @@
         <v>1453</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>8109</v>
+        <v>8108</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2077,20 +2077,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1267</v>
+        <v>1252</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1617411</v>
+        <v>1617248</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1622</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2113,14 +2113,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2144,17 +2144,17 @@
         <v>1622</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1621718</v>
+        <v>1621555</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3243</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>3243</v>
@@ -2208,17 +2208,17 @@
         <v>3243</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17472</v>
+        <v>17471</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2262,17 +2262,17 @@
         <v>649</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1621718</v>
+        <v>1621555</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1297</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>1587664</v>
+        <v>1587504</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>4865</v>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>648687</v>
+        <v>648622</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1622</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2229</v>
+        <v>2160</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
         <v>2421</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>13138</v>
+        <v>13136</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3243</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3717</v>
+        <v>3778</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3392</v>
+        <v>3405</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2515,20 +2515,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3777</v>
+        <v>3394</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21678</v>
+        <v>21675</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2547,18 +2547,18 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2579,20 +2579,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>31346</v>
+        <v>31343</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
         <v>950</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1622</v>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2702,17 +2702,17 @@
         <v>1622</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>4262</v>
+        <v>4261</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>3243</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
         <v>9</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2762,17 +2762,17 @@
         <v>3243</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>324344</v>
+        <v>324311</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>2522</v>
+        <v>1623</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>148463</v>
+        <v>148449</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3243</v>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2887,20 +2887,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>4640</v>
+        <v>7597</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17841</v>
+        <v>17839</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2919,11 +2919,11 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -2951,20 +2951,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15515</v>
+        <v>15513</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -2983,18 +2983,18 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>2820</v>
+        <v>1939</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3356</v>
+        <v>3001</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3014,17 +3014,17 @@
         <v>3811</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6281</v>
+        <v>6280</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>3101</v>
+        <v>2617</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6403</v>
+        <v>6402</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>6</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>5368</v>
+        <v>5367</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3071,10 +3071,10 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>9114</v>
+        <v>9113</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>6094</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3103,18 +3103,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>10676</v>
+        <v>10589</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>40</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9639</v>
+        <v>9669</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3131,20 +3131,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>10587</v>
+        <v>9707</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>10684</v>
+        <v>10683</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10681</v>
+        <v>10808</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
         <v>1622</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8941</v>
+        <v>8940</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>3243</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3252,17 +3252,17 @@
         <v>3243</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
         <v>795</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>6023</v>
+        <v>6022</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>811</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3377,20 +3377,20 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>968</v>
+        <v>1052</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>1622</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="n">
-        <v>2193</v>
+        <v>1943</v>
       </c>
       <c r="M50" s="3" t="n">
         <v>4252</v>
@@ -3500,11 +3500,11 @@
         <v>1784</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>4473</v>
+        <v>4472</v>
       </c>
       <c r="M51" s="3" t="n">
         <v>4474</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3601,10 +3601,10 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>3243</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="L53" s="3" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4945</v>
+        <v>4944</v>
       </c>
       <c r="N53" s="3" t="n">
         <v>811</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
         <v>1849</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11581</v>
+        <v>11580</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1622</v>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
         <v>4865</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>31369</v>
+        <v>31366</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3243</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>10186</v>
+        <v>10185</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>13</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>9028</v>
+        <v>9027</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3847,20 +3847,20 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>12108</v>
+        <v>12107</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>12108</v>
+        <v>12107</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>10249</v>
+        <v>10248</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3879,18 +3879,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>14469</v>
+        <v>13718</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>13517</v>
+        <v>13654</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3911,20 +3911,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>15260</v>
+        <v>15097</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>31409</v>
+        <v>31406</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>15946</v>
+        <v>15945</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>5627</v>
+        <v>3781</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>38</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>4476</v>
+        <v>4490</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3975,20 +3975,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>5819</v>
+        <v>5525</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10587</v>
+        <v>10586</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>5095</v>
+        <v>5017</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4007,18 +4007,18 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>4176</v>
+        <v>4847</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3385</v>
+        <v>3466</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4039,20 +4039,20 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>4249</v>
+        <v>4853</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11595</v>
+        <v>11594</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>4551</v>
+        <v>4728</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4203,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>10055</v>
+        <v>10054</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4249,20 +4249,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4305,12 +4305,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4351,20 +4351,20 @@
         </is>
       </c>
       <c r="L65" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>43786</v>
+        <v>43782</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4405,20 +4405,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>51895</v>
+        <v>51890</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4459,20 +4459,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>9082</v>
+        <v>9081</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22704</v>
+        <v>22702</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4515,12 +4515,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22704</v>
+        <v>22702</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4685,14 +4685,14 @@
         <v>5157</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4733,20 +4733,20 @@
         </is>
       </c>
       <c r="L72" s="3" t="n">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1521240</v>
+        <v>1521087</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11676</v>
+        <v>11675</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4790,17 +4790,17 @@
         <v>4873</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7666</v>
+        <v>7665</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9730</v>
+        <v>9729</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4844,17 +4844,17 @@
         <v>8919</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21486</v>
+        <v>21484</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17839</v>
+        <v>17837</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4895,20 +4895,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17839</v>
+        <v>17837</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27735</v>
+        <v>27732</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -4959,20 +4959,20 @@
         </is>
       </c>
       <c r="L76" s="3" t="n">
-        <v>162</v>
+        <v>253</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6536</v>
+        <v>6535</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
         <v>1216</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5318</v>
+        <v>5317</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>950</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5141,14 +5141,14 @@
         <v>5838</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="O79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5237,20 +5237,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23719</v>
+        <v>23717</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23719</v>
+        <v>23717</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10379</v>
+        <v>10378</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5293,12 +5293,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20758</v>
+        <v>20756</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5321,14 +5321,14 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>162</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1621556</v>
+        <v>1621393</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>811</v>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5405,20 +5405,20 @@
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="3" t="n">
-        <v>975</v>
+        <v>777</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>35451</v>
+        <v>35447</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1622</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
         <v>2309</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>3243</v>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5518,17 +5518,17 @@
         <v>5037</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10379</v>
+        <v>10378</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5611,12 +5611,12 @@
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>14595</v>
+        <v>14594</v>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17839</v>
+        <v>17837</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
         <v>195</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>88137</v>
+        <v>88128</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>811</v>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>1</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>843</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>5391</v>
+        <v>5390</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>1622</v>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5913,12 +5913,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10379</v>
+        <v>10378</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14595</v>
+        <v>14594</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6001,12 +6001,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17839</v>
+        <v>17837</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
         <v>1641</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="N97" s="3" t="n">
         <v>2919</v>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6158,17 +6158,17 @@
         <v>4054</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>5308</v>
+        <v>5307</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>10055</v>
+        <v>10054</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6209,20 +6209,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6265,12 +6265,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6311,20 +6311,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>18424</v>
+        <v>18422</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>18424</v>
+        <v>18422</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>43786</v>
+        <v>43782</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6367,12 +6367,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>51895</v>
+        <v>51890</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6517,12 +6517,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>10055</v>
+        <v>10054</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6563,20 +6563,20 @@
         </is>
       </c>
       <c r="L107" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O107" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>43786</v>
+        <v>43782</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6715,12 +6715,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>51895</v>
+        <v>51890</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6761,20 +6761,20 @@
         </is>
       </c>
       <c r="L111" s="3" t="n">
-        <v>96839</v>
+        <v>75548</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>96839</v>
+        <v>75548</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>81086</v>
+        <v>81078</v>
       </c>
       <c r="O111" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>89195</v>
+        <v>89186</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>89195</v>
+        <v>89186</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6825,20 +6825,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>89195</v>
+        <v>89186</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>99564</v>
+        <v>99554</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>113520</v>
+        <v>113509</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6879,20 +6879,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>113520</v>
+        <v>113509</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>113520</v>
+        <v>113509</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>145955</v>
+        <v>145940</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6943,20 +6943,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -6974,13 +6974,23 @@
           <t>乗り物 / 輸送機</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr"/>
-      <c r="E115" s="2" t="inlineStr"/>
-      <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="3" t="inlineStr"/>
+      <c r="D115" s="3" t="n">
+        <v>162156</v>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>162156</v>
+      </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
@@ -6997,20 +7007,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>194606</v>
+        <v>194587</v>
       </c>
       <c r="O115" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7051,20 +7061,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>218932</v>
+        <v>218910</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>291909</v>
+        <v>291880</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>259475</v>
+        <v>259449</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7128,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7169,7 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>5997</v>
@@ -7172,7 +7182,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7225,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>8109</v>
+        <v>8108</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7261,20 +7271,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14595</v>
+        <v>14594</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14595</v>
+        <v>14594</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7317,12 +7327,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>23353</v>
+        <v>23350</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7363,20 +7373,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>19500</v>
+        <v>19498</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7417,20 +7427,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>32434369</v>
+        <v>32431103</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7494,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7538,7 @@
         <v>2293</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>5824</v>
+        <v>5823</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>4054</v>
@@ -7538,7 +7548,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7579,20 +7589,20 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>6623</v>
+        <v>6622</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6623</v>
+        <v>6622</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>8109</v>
+        <v>8108</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7633,20 +7643,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>12184</v>
+        <v>12183</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14595</v>
+        <v>14594</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7689,12 +7699,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>23353</v>
+        <v>23350</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7737,12 +7747,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7800,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7830,7 @@
         <v>2</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>4164</v>
+        <v>4163</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -7847,14 +7857,14 @@
         <v>3243</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O131" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7895,20 +7905,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -7949,20 +7959,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9730</v>
+        <v>9729</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>16306</v>
+        <v>16305</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8005,12 +8015,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>29191</v>
+        <v>29188</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8051,20 +8061,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21893</v>
+        <v>21891</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21893</v>
+        <v>21891</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>48652</v>
+        <v>48647</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8093,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>29191</v>
+        <v>29188</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8094,7 +8104,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>29191</v>
+        <v>29188</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8115,20 +8125,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>29191</v>
+        <v>29188</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>29191</v>
+        <v>29188</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>72977</v>
+        <v>72970</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8169,20 +8179,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8201,18 +8211,18 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8233,20 +8243,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>13066</v>
+        <v>13065</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8320,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8329,18 +8339,18 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8361,20 +8371,20 @@
         </is>
       </c>
       <c r="L140" s="3" t="n">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>5295</v>
+        <v>5294</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8448,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8512,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8566,7 @@
         <v>2124</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="N143" s="3" t="n">
         <v>3243</v>
@@ -8566,7 +8576,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8630,7 @@
         <v>2426</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>11008</v>
+        <v>11007</v>
       </c>
       <c r="N144" s="3" t="n">
         <v>4054</v>
@@ -8630,7 +8640,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8688,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8707,7 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>4541</v>
+        <v>4540</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -8708,7 +8718,7 @@
         <v>1</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>4541</v>
+        <v>4540</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -8729,20 +8739,20 @@
         </is>
       </c>
       <c r="L146" s="3" t="n">
-        <v>4541</v>
+        <v>4540</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>54843</v>
+        <v>54838</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8785,12 +8795,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8831,20 +8841,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9730</v>
+        <v>9729</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17771</v>
+        <v>17769</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8887,12 +8897,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25947</v>
+        <v>25945</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8911,18 +8921,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>16376</v>
+        <v>16378</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8943,20 +8953,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>40543</v>
+        <v>40539</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8985,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -8983,10 +8993,10 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9007,20 +9017,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>86178</v>
+        <v>86169</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>77842</v>
+        <v>77835</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9061,20 +9071,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>105412</v>
+        <v>105401</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>105412</v>
+        <v>105401</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>210823</v>
+        <v>210802</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9128,17 +9138,17 @@
         <v>162</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10609</v>
+        <v>10608</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9212,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9262,7 @@
         <v>811</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15890</v>
+        <v>15888</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1622</v>
@@ -9262,7 +9272,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9318,11 +9328,11 @@
         <v>3243</v>
       </c>
       <c r="O156" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9372,17 +9382,17 @@
         <v>3243</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9436,7 @@
         <v>811</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>19826</v>
+        <v>19824</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1622</v>
@@ -9436,7 +9446,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9490,7 @@
         <v>1622</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19667</v>
+        <v>19665</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3243</v>
@@ -9490,7 +9500,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9544,17 +9554,17 @@
         <v>3243</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6547</v>
+        <v>6546</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O160" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9618,7 +9628,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9669,10 +9679,10 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30942</v>
+        <v>30939</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1622</v>
@@ -9682,7 +9692,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9739,14 +9749,14 @@
         <v>3892</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="O163" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9765,18 +9775,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3967</v>
+        <v>3733</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
         <v>56</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3674</v>
+        <v>3662</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9797,20 +9807,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>4079</v>
+        <v>3777</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9884,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9948,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -9957,18 +9967,18 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>1549</v>
+        <v>739</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>1527</v>
+        <v>1429</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -9992,17 +10002,17 @@
         <v>1455</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9967</v>
+        <v>9966</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>1701</v>
+        <v>1406</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10076,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10130,7 @@
         <v>221</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>324</v>
@@ -10130,7 +10140,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10171,20 +10181,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>97303</v>
+        <v>97293</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>97303</v>
+        <v>97293</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10227,12 +10237,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>43786</v>
+        <v>43782</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10292,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10332,7 @@
         <v>2108</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="N173" s="3" t="n">
         <v>4054</v>
@@ -10332,7 +10342,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10371,12 +10381,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>8109</v>
+        <v>8108</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10413,20 +10423,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>8519</v>
+        <v>14563</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14595</v>
+        <v>14594</v>
       </c>
       <c r="O175" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10463,20 +10473,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11676</v>
+        <v>11675</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11676</v>
+        <v>11675</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>23353</v>
+        <v>23350</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10513,20 +10523,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>16298</v>
+        <v>16297</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10563,20 +10573,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19623</v>
+        <v>19621</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>27</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10634,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10665,20 +10675,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10721,12 +10731,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10767,20 +10777,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9730</v>
+        <v>9729</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9730</v>
+        <v>9729</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10823,12 +10833,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>29191</v>
+        <v>29188</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10869,20 +10879,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21893</v>
+        <v>21891</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21893</v>
+        <v>21891</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>43786</v>
+        <v>43782</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10923,20 +10933,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>29191</v>
+        <v>29188</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>29191</v>
+        <v>29188</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>58382</v>
+        <v>58376</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10990,17 @@
         <v>162</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11034,17 +11044,17 @@
         <v>162</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O187" s="2" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11088,17 +11098,17 @@
         <v>162</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>105512</v>
+        <v>105502</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O188" s="2" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11156,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11200,17 +11210,17 @@
         <v>162</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29911</v>
+        <v>29908</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11264,17 +11274,17 @@
         <v>162</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>160117</v>
+        <v>160101</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11318,17 +11328,17 @@
         <v>162</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11386,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11420,17 +11430,17 @@
         <v>162</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11484,17 +11494,17 @@
         <v>162</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>162010</v>
+        <v>161993</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11538,17 +11548,17 @@
         <v>162</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11596,7 +11606,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11647,20 +11657,20 @@
         </is>
       </c>
       <c r="L198" s="3" t="n">
-        <v>923</v>
+        <v>874</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>582</v>
       </c>
       <c r="O198" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11689,7 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
@@ -11690,7 +11700,7 @@
         <v>1</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -11711,20 +11721,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>21118</v>
+        <v>21116</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>21118</v>
+        <v>21116</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11765,20 +11775,20 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>4541</v>
+        <v>4540</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6466</v>
+        <v>6465</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11822,17 +11832,17 @@
         <v>5189</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>11049</v>
+        <v>11048</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7784</v>
+        <v>7783</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11873,20 +11883,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M202" s="3" t="n">
         <v>8092</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10379</v>
+        <v>10378</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11927,20 +11937,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8433</v>
+        <v>8432</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>283103</v>
+        <v>283075</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>14271</v>
+        <v>14270</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -11981,20 +11991,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>16024</v>
+        <v>16023</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16447</v>
+        <v>16446</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12013,7 +12023,7 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>21762</v>
+        <v>21760</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
@@ -12024,7 +12034,7 @@
         <v>2</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>21260</v>
+        <v>21258</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -12045,20 +12055,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>23374</v>
+        <v>23371</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>50028</v>
+        <v>50023</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12101,12 +12111,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>23353</v>
+        <v>23350</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12170,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12211,7 +12221,7 @@
         </is>
       </c>
       <c r="L208" s="3" t="n">
-        <v>963</v>
+        <v>582</v>
       </c>
       <c r="M208" s="3" t="n">
         <v>1622</v>
@@ -12220,11 +12230,11 @@
         <v>324</v>
       </c>
       <c r="O208" s="2" t="n">
-        <v>918</v>
+        <v>948</v>
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12288,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12332,7 @@
         <v>2108</v>
       </c>
       <c r="M210" s="3" t="n">
-        <v>4585</v>
+        <v>4584</v>
       </c>
       <c r="N210" s="3" t="n">
         <v>4216</v>
@@ -12332,7 +12342,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12376,17 +12386,17 @@
         <v>4054</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>8109</v>
+        <v>8108</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>8109</v>
+        <v>8108</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12427,20 +12437,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14595</v>
+        <v>14594</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12483,12 +12493,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>23353</v>
+        <v>23350</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12529,20 +12539,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12586,17 +12596,17 @@
         <v>1135</v>
       </c>
       <c r="M215" s="3" t="n">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="N215" s="3" t="n">
         <v>2270</v>
       </c>
       <c r="O215" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12650,7 @@
         <v>2108</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>12177</v>
+        <v>12176</v>
       </c>
       <c r="N216" s="3" t="n">
         <v>4216</v>
@@ -12650,7 +12660,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12691,20 +12701,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15967</v>
+        <v>15966</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>21922</v>
+        <v>21920</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25947</v>
+        <v>25945</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12748,17 +12758,17 @@
         <v>4054</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>7883</v>
+        <v>7882</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>8109</v>
+        <v>8108</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12799,20 +12809,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7298</v>
+        <v>7297</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14595</v>
+        <v>14594</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12855,12 +12865,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12901,20 +12911,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -12944,7 +12954,7 @@
         <v>2</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -12968,17 +12978,17 @@
         <v>970</v>
       </c>
       <c r="M222" s="3" t="n">
-        <v>2329</v>
+        <v>2912</v>
       </c>
       <c r="N222" s="3" t="n">
         <v>1622</v>
       </c>
       <c r="O222" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13038,11 +13048,11 @@
         <v>3243</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13099,14 +13109,14 @@
         <v>7380</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O224" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13170,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13211,7 +13221,7 @@
         </is>
       </c>
       <c r="L226" s="3" t="n">
-        <v>3125</v>
+        <v>1622</v>
       </c>
       <c r="M226" s="3" t="n">
         <v>3563</v>
@@ -13220,11 +13230,11 @@
         <v>3243</v>
       </c>
       <c r="O226" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13278,17 @@
         <v>3243</v>
       </c>
       <c r="M227" s="3" t="n">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O227" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13342,7 @@
         <v>162</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>324</v>
@@ -13342,7 +13352,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13386,17 +13396,17 @@
         <v>162</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13450,17 +13460,17 @@
         <v>162</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13504,17 +13514,17 @@
         <v>811</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1622</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13578,7 +13588,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13622,17 +13632,17 @@
         <v>3243</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7389</v>
+        <v>7388</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O233" s="2" t="n">
         <v>35</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13696,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13740,17 +13750,17 @@
         <v>4036</v>
       </c>
       <c r="M235" s="3" t="n">
-        <v>4036</v>
+        <v>4370</v>
       </c>
       <c r="N235" s="3" t="n">
         <v>3243</v>
       </c>
       <c r="O235" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13779,7 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>5125</v>
+        <v>5124</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -13777,10 +13787,10 @@
         </is>
       </c>
       <c r="F236" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>4168</v>
+        <v>5124</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -13804,7 +13814,7 @@
         <v>5139</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6688</v>
+        <v>6687</v>
       </c>
       <c r="N236" s="3" t="n">
         <v>5637</v>
@@ -13814,7 +13824,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13862,7 +13872,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13906,17 +13916,17 @@
         <v>8919</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11305</v>
+        <v>11304</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -13959,12 +13969,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14005,20 +14015,20 @@
         </is>
       </c>
       <c r="L240" s="3" t="n">
-        <v>10742</v>
+        <v>10741</v>
       </c>
       <c r="M240" s="3" t="n">
-        <v>10742</v>
+        <v>10741</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O240" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14047,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>19063</v>
+        <v>19061</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -14048,7 +14058,7 @@
         <v>10</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>19315</v>
+        <v>19313</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -14068,21 +14078,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L241" s="3" t="n">
-        <v>25703</v>
-      </c>
-      <c r="M241" s="3" t="n">
-        <v>25703</v>
-      </c>
+      <c r="L241" s="3" t="inlineStr"/>
+      <c r="M241" s="3" t="inlineStr"/>
       <c r="N241" s="3" t="n">
-        <v>32434</v>
-      </c>
-      <c r="O241" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>32431</v>
+      </c>
+      <c r="O241" s="2" t="inlineStr"/>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14101,18 +14105,18 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14133,20 +14137,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>43765</v>
+        <v>40779</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>60088</v>
+        <v>60082</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>77842</v>
+        <v>77835</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14165,18 +14169,18 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>16217</v>
+        <v>17454</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>19808</v>
+        <v>19668</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14193,20 +14197,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>17456</v>
+        <v>20458</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>32434369</v>
+        <v>32431103</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14249,12 +14253,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25947</v>
+        <v>25945</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14308,7 +14312,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14335,10 +14339,10 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2887</v>
+        <v>2880</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14359,20 +14363,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>3136</v>
+        <v>2648</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N246" s="3" t="n">
         <v>3271</v>
       </c>
       <c r="O246" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14413,20 +14417,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>9082</v>
+        <v>15924</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23911</v>
+        <v>23908</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>18163</v>
+        <v>18161</v>
       </c>
       <c r="O247" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14445,7 +14449,7 @@
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>9082</v>
+        <v>9081</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -14456,7 +14460,7 @@
         <v>1</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>9082</v>
+        <v>9081</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -14477,20 +14481,20 @@
         </is>
       </c>
       <c r="L248" s="3" t="n">
-        <v>9082</v>
+        <v>9081</v>
       </c>
       <c r="M248" s="3" t="n">
-        <v>9082</v>
+        <v>9081</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>18163</v>
+        <v>18161</v>
       </c>
       <c r="O248" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14530,17 +14534,17 @@
         <v>811</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9521</v>
+        <v>9520</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1622</v>
       </c>
       <c r="O249" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14590,7 +14594,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14644,7 +14648,7 @@
         <v>162</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>99721</v>
+        <v>99711</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>324</v>
@@ -14654,7 +14658,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14695,20 +14699,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>51674</v>
+        <v>51669</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>51674</v>
+        <v>51669</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O252" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14749,20 +14753,20 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>6829</v>
+        <v>6828</v>
       </c>
       <c r="M253" s="3" t="n">
         <v>7732</v>
       </c>
       <c r="N253" s="3" t="n">
-        <v>7784</v>
+        <v>7783</v>
       </c>
       <c r="O253" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14781,7 +14785,7 @@
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
@@ -14792,7 +14796,7 @@
         <v>1</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -14813,20 +14817,20 @@
         </is>
       </c>
       <c r="L254" s="3" t="n">
-        <v>6852</v>
+        <v>6851</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>194606</v>
+        <v>194587</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>10379</v>
+        <v>10378</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14890,7 +14894,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14934,7 +14938,7 @@
         <v>389</v>
       </c>
       <c r="M256" s="3" t="n">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="N256" s="3" t="n">
         <v>324</v>
@@ -14944,7 +14948,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -14988,7 +14992,7 @@
         <v>298</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>8109</v>
+        <v>8108</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>324</v>
@@ -14998,7 +15002,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15017,11 +15021,11 @@
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>2590</v>
+        <v>324</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
@@ -15058,11 +15062,11 @@
         <v>649</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>364</v>
+        <v>266</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15116,7 +15120,7 @@
         <v>1359</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21930</v>
+        <v>21928</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1622</v>
@@ -15126,7 +15130,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15180,7 +15184,7 @@
         <v>2643</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="N260" s="3" t="n">
         <v>3243</v>
@@ -15190,7 +15194,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15213,7 @@
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -15220,7 +15224,7 @@
         <v>2</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -15244,17 +15248,17 @@
         <v>3243</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>7194</v>
+        <v>7193</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O261" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15273,18 +15277,18 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6487</v>
+        <v>6488</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F262" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6515</v>
+        <v>6514</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15305,20 +15309,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15366,7 @@
         <v>811</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10830</v>
+        <v>10829</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1622</v>
@@ -15372,7 +15376,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15436,7 +15440,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15489,12 +15493,12 @@
       <c r="L265" s="3" t="inlineStr"/>
       <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15517,7 @@
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -15521,10 +15525,10 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -15545,20 +15549,20 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>9883</v>
+        <v>9882</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9883</v>
+        <v>9882</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15612,17 +15616,17 @@
         <v>2757</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19946</v>
+        <v>19944</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="O267" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15641,7 +15645,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8433</v>
+        <v>8432</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15652,7 +15656,7 @@
         <v>2</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>8433</v>
+        <v>8432</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15673,20 +15677,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>8433</v>
+        <v>8432</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14608</v>
+        <v>14607</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>14271</v>
+        <v>14270</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15729,12 +15733,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15775,20 +15779,20 @@
         </is>
       </c>
       <c r="L270" s="3" t="n">
-        <v>25536</v>
+        <v>25533</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>25536</v>
+        <v>25533</v>
       </c>
       <c r="N270" s="3" t="n">
-        <v>25947</v>
+        <v>25945</v>
       </c>
       <c r="O270" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15807,7 +15811,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>34084</v>
+        <v>34080</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15818,7 +15822,7 @@
         <v>2</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>27421</v>
+        <v>27418</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15839,20 +15843,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>36646</v>
+        <v>41747</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>36646</v>
+        <v>41747</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15896,7 +15900,7 @@
         <v>162</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>9952</v>
+        <v>9951</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>324</v>
@@ -15906,7 +15910,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -15950,7 +15954,7 @@
         <v>162</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21478</v>
+        <v>21476</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>324</v>
@@ -15960,7 +15964,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16014,17 +16018,17 @@
         <v>162</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>32541</v>
+        <v>32538</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O274" s="2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16078,17 +16082,17 @@
         <v>162</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>16298</v>
+        <v>16297</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O275" s="2" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16107,18 +16111,18 @@
         </is>
       </c>
       <c r="D276" s="3" t="n">
-        <v>162</v>
+        <v>13726</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>162</v>
+        <v>4684</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -16142,17 +16146,17 @@
         <v>162</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>162169</v>
+        <v>162152</v>
       </c>
       <c r="N276" s="3" t="n">
-        <v>324</v>
+        <v>15098</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16206,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16225,7 @@
         </is>
       </c>
       <c r="D278" s="3" t="n">
-        <v>4541</v>
+        <v>4540</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
@@ -16232,7 +16236,7 @@
         <v>1</v>
       </c>
       <c r="G278" s="3" t="n">
-        <v>4541</v>
+        <v>4540</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -16253,20 +16257,20 @@
         </is>
       </c>
       <c r="L278" s="3" t="n">
-        <v>4541</v>
+        <v>4540</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>8749</v>
+        <v>8748</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O278" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16310,17 +16314,17 @@
         <v>5189</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>10147</v>
+        <v>10146</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7784</v>
+        <v>7783</v>
       </c>
       <c r="O279" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16361,20 +16365,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="M280" s="3" t="n">
         <v>8825</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10379</v>
+        <v>10378</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16417,12 +16421,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>14271</v>
+        <v>14270</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16465,12 +16469,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16513,12 +16517,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25947</v>
+        <v>25945</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16537,7 +16541,7 @@
         </is>
       </c>
       <c r="D284" s="3" t="n">
-        <v>20758</v>
+        <v>20756</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
@@ -16548,7 +16552,7 @@
         <v>1</v>
       </c>
       <c r="G284" s="3" t="n">
-        <v>20758</v>
+        <v>20756</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -16569,20 +16573,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>28867</v>
+        <v>34053</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>28867</v>
+        <v>34053</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16605,7 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>9708</v>
+        <v>9707</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
@@ -16612,7 +16616,7 @@
         <v>13</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>10168</v>
+        <v>10167</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16633,20 +16637,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>10645</v>
+        <v>10478</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>10677</v>
+        <v>10676</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16714,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16729,18 +16733,18 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5061</v>
+        <v>5343</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5079</v>
+        <v>5097</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16763,14 +16767,14 @@
         <v>5919</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>4713</v>
+        <v>4707</v>
       </c>
       <c r="O287" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16789,18 +16793,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>6649</v>
+        <v>6679</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6813</v>
+        <v>6811</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16817,20 +16821,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>6785</v>
+        <v>7072</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>8037</v>
+        <v>8036</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7565</v>
+        <v>7422</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16849,18 +16853,18 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>9708</v>
+        <v>8252</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9400</v>
+        <v>9361</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16877,20 +16881,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9698</v>
+        <v>9519</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11788</v>
+        <v>11787</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>10402</v>
+        <v>10177</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -16920,7 +16924,7 @@
         <v>4</v>
       </c>
       <c r="G290" s="3" t="n">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -16954,7 +16958,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17005,7 +17009,7 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>2426</v>
+        <v>2531</v>
       </c>
       <c r="M291" s="3" t="n">
         <v>5189</v>
@@ -17018,7 +17022,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17052,7 @@
         <v>8</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4456</v>
+        <v>4455</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -17069,20 +17073,20 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>4186</v>
+        <v>4185</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5676</v>
+        <v>5675</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O292" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17146,7 +17150,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17165,18 +17169,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>6733</v>
+        <v>6018</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>6822</v>
+        <v>6791</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17197,20 +17201,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>6305</v>
+        <v>5786</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>19358</v>
+        <v>19357</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>7805</v>
+        <v>7398</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17251,20 +17255,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>52711</v>
+        <v>52705</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>716380</v>
+        <v>716307</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>40543</v>
+        <v>40539</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17287,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17294,7 +17298,7 @@
         <v>11</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17315,20 +17319,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>70511</v>
+        <v>70504</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>40543</v>
+        <v>40539</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17351,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>64869</v>
+        <v>64862</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17358,7 +17362,7 @@
         <v>6</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>64869</v>
+        <v>64862</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17379,20 +17383,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>64869</v>
+        <v>64862</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>81086</v>
+        <v>81078</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17411,7 +17415,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17419,10 +17423,10 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17443,20 +17447,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>129737</v>
+        <v>129724</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>129741</v>
+        <v>129728</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>162172</v>
+        <v>162156</v>
       </c>
       <c r="O298" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17475,7 +17479,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>259475</v>
+        <v>259449</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17486,7 +17490,7 @@
         <v>2</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>259475</v>
+        <v>259449</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17507,20 +17511,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>259475</v>
+        <v>259449</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>261974</v>
+        <v>261948</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>324344</v>
+        <v>324311</v>
       </c>
       <c r="O299" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17543,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>454081</v>
+        <v>454035</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17547,10 +17551,10 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>454671</v>
+        <v>454035</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17571,20 +17575,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>454081</v>
+        <v>454035</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>973857</v>
+        <v>973758</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>648687</v>
+        <v>648622</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17603,18 +17607,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>12615</v>
+        <v>16966</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>19607</v>
+        <v>19365</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17635,20 +17639,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>17435</v>
+        <v>34215</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>34218</v>
+        <v>34215</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>16264</v>
+        <v>17463</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17667,18 +17671,18 @@
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>1451</v>
+        <v>1939</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F302" s="2" t="n">
         <v>11</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1802</v>
+        <v>1684</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17699,10 +17703,10 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>1940</v>
+        <v>1951</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>4919</v>
+        <v>4918</v>
       </c>
       <c r="N302" s="3" t="n">
         <v>2270</v>
@@ -17712,7 +17716,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17742,7 +17746,7 @@
         <v>16</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4257</v>
+        <v>4256</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17763,20 +17767,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4327</v>
+        <v>4391</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>16216</v>
+        <v>16214</v>
       </c>
       <c r="N303" s="3" t="n">
         <v>4719</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17803,10 +17807,10 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1659</v>
+        <v>1733</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17827,10 +17831,10 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>1941</v>
+        <v>1455</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>11352</v>
+        <v>11351</v>
       </c>
       <c r="N304" s="3" t="n">
         <v>2270</v>
@@ -17840,7 +17844,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17904,7 +17908,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -17923,7 +17927,7 @@
         </is>
       </c>
       <c r="D306" s="3" t="n">
-        <v>10050</v>
+        <v>10049</v>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
@@ -17958,17 +17962,17 @@
         <v>162</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>16565</v>
+        <v>16566</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18019,10 +18023,10 @@
         </is>
       </c>
       <c r="L307" s="3" t="n">
-        <v>1404</v>
+        <v>1398</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>324</v>
@@ -18032,7 +18036,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18055,11 +18059,11 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G308" s="3" t="n">
         <v>2108</v>
@@ -18086,17 +18090,17 @@
         <v>2108</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1297375</v>
+        <v>1297244</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>4054</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18137,20 +18141,20 @@
         </is>
       </c>
       <c r="L309" s="3" t="n">
-        <v>4541</v>
+        <v>4540</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>32791</v>
+        <v>32788</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6487</v>
+        <v>6486</v>
       </c>
       <c r="O309" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18204,7 +18208,7 @@
         <v>1622</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>6179</v>
+        <v>6178</v>
       </c>
       <c r="N310" s="3" t="n">
         <v>3243</v>
@@ -18214,7 +18218,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18265,7 +18269,7 @@
         </is>
       </c>
       <c r="L311" s="3" t="n">
-        <v>4966</v>
+        <v>4965</v>
       </c>
       <c r="M311" s="3" t="n">
         <v>6188</v>
@@ -18278,7 +18282,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18321,12 +18325,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12974</v>
+        <v>12972</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18349,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9730</v>
+        <v>9729</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18356,7 +18360,7 @@
         <v>1</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9730</v>
+        <v>9729</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18377,20 +18381,20 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9730</v>
+        <v>9729</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26813</v>
+        <v>26811</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>19461</v>
+        <v>19459</v>
       </c>
       <c r="O313" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18431,20 +18435,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15865</v>
+        <v>15864</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15865</v>
+        <v>15864</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25947</v>
+        <v>25945</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18463,18 +18467,18 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>16278</v>
+        <v>16274</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18495,20 +18499,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1621718</v>
+        <v>1621555</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>32434</v>
+        <v>32431</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18527,7 +18531,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18538,7 +18542,7 @@
         <v>4</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18559,20 +18563,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>38921</v>
+        <v>38917</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>77842</v>
+        <v>77835</v>
       </c>
       <c r="O316" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18613,20 +18617,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>105412</v>
+        <v>105401</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>105412</v>
+        <v>105401</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>210823</v>
+        <v>210802</v>
       </c>
       <c r="O317" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18645,18 +18649,18 @@
         </is>
       </c>
       <c r="D318" s="3" t="n">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>811</v>
+        <v>836</v>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
@@ -18677,20 +18681,20 @@
         </is>
       </c>
       <c r="L318" s="3" t="n">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="M318" s="3" t="n">
         <v>2103</v>
       </c>
       <c r="N318" s="3" t="n">
-        <v>324</v>
+        <v>973</v>
       </c>
       <c r="O318" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18744,7 +18748,7 @@
         <v>1438</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>16107</v>
+        <v>16105</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>324</v>
@@ -18754,7 +18758,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18808,7 +18812,7 @@
         <v>1135</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>10076</v>
+        <v>10075</v>
       </c>
       <c r="N320" s="3" t="n">
         <v>2270</v>
@@ -18818,7 +18822,7 @@
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18869,7 +18873,7 @@
         </is>
       </c>
       <c r="L321" s="3" t="n">
-        <v>4054</v>
+        <v>3730</v>
       </c>
       <c r="M321" s="3" t="n">
         <v>6031</v>
@@ -18878,11 +18882,11 @@
         <v>324</v>
       </c>
       <c r="O321" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18950,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -18965,18 +18969,18 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>4114</v>
+        <v>1939</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>3471</v>
+        <v>3216</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -19000,17 +19004,17 @@
         <v>2924</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>16919</v>
+        <v>16918</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>4059</v>
+        <v>3674</v>
       </c>
       <c r="O323" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19064,7 +19068,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19087,7 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
@@ -19091,10 +19095,10 @@
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>1822</v>
+        <v>1801</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -19118,7 +19122,7 @@
         <v>2329</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>16107</v>
+        <v>16105</v>
       </c>
       <c r="N325" s="3" t="n">
         <v>2517</v>
@@ -19128,7 +19132,7 @@
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19158,7 +19162,7 @@
         <v>9</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -19182,7 +19186,7 @@
         <v>1904</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="N326" s="3" t="n">
         <v>2270</v>
@@ -19192,7 +19196,7 @@
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19211,18 +19215,18 @@
         </is>
       </c>
       <c r="D327" s="3" t="n">
-        <v>3112</v>
+        <v>4659</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>3616</v>
+        <v>3720</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19243,20 +19247,20 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>3840</v>
+        <v>3738</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>11352</v>
+        <v>11351</v>
       </c>
       <c r="N327" s="3" t="n">
-        <v>2883</v>
+        <v>3631</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19275,7 +19279,7 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>22633</v>
+        <v>22630</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
@@ -19283,10 +19287,10 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>20846</v>
+        <v>20821</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19307,20 +19311,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>26775</v>
+        <v>26211</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>33425</v>
+        <v>33422</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>22093</v>
+        <v>22090</v>
       </c>
       <c r="O328" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19339,18 +19343,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>6735</v>
+        <v>6785</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7511</v>
+        <v>7464</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19371,20 +19375,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>6789</v>
+        <v>6697</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9330</v>
+        <v>9329</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8152</v>
+        <v>8035</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19403,18 +19407,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>6396</v>
+        <v>6600</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>6203</v>
+        <v>6197</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19435,20 +19439,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>6576</v>
+        <v>6584</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8874</v>
+        <v>8873</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6244</v>
+        <v>6770</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19467,7 +19471,7 @@
         </is>
       </c>
       <c r="D331" s="3" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
@@ -19499,20 +19503,20 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1584</v>
+        <v>1453</v>
       </c>
       <c r="M331" s="3" t="n">
         <v>3243</v>
       </c>
       <c r="N331" s="3" t="n">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="O331" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19563,20 +19567,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1148</v>
+        <v>970</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N332" s="3" t="n">
         <v>1262</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19627,20 +19631,20 @@
         </is>
       </c>
       <c r="L333" s="3" t="n">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="M333" s="3" t="n">
-        <v>4953</v>
+        <v>4952</v>
       </c>
       <c r="N333" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O333" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19691,20 +19695,20 @@
         </is>
       </c>
       <c r="L334" s="3" t="n">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>514</v>
       </c>
       <c r="O334" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19734,7 +19738,7 @@
         <v>8</v>
       </c>
       <c r="G335" s="3" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
@@ -19755,7 +19759,7 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>2133</v>
+        <v>1938</v>
       </c>
       <c r="M335" s="3" t="n">
         <v>4946</v>
@@ -19764,11 +19768,11 @@
         <v>2270</v>
       </c>
       <c r="O335" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19832,7 +19836,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19851,18 +19855,18 @@
         </is>
       </c>
       <c r="D337" s="3" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
@@ -19886,17 +19890,17 @@
         <v>162</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15878</v>
+        <v>15877</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>324</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>685</v>
+        <v>575</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -19947,7 +19951,7 @@
         </is>
       </c>
       <c r="L338" s="3" t="n">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="M338" s="3" t="n">
         <v>1004</v>
@@ -19956,11 +19960,11 @@
         <v>341</v>
       </c>
       <c r="O338" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -20011,7 +20015,7 @@
         </is>
       </c>
       <c r="L339" s="3" t="n">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="M339" s="3" t="n">
         <v>4829</v>
@@ -20020,11 +20024,11 @@
         <v>514</v>
       </c>
       <c r="O339" s="2" t="n">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20047,7 @@
         </is>
       </c>
       <c r="D340" s="3" t="n">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
@@ -20054,7 +20058,7 @@
         <v>1</v>
       </c>
       <c r="G340" s="3" t="n">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
@@ -20088,7 +20092,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -20139,20 +20143,20 @@
         </is>
       </c>
       <c r="L341" s="3" t="n">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M341" s="3" t="n">
         <v>2450</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -20206,7 +20210,7 @@
         <v>647</v>
       </c>
       <c r="M342" s="3" t="n">
-        <v>16217</v>
+        <v>16216</v>
       </c>
       <c r="N342" s="3" t="n">
         <v>478</v>
@@ -20216,7 +20220,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -20267,10 +20271,10 @@
         </is>
       </c>
       <c r="L343" s="3" t="n">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M343" s="3" t="n">
-        <v>16217</v>
+        <v>757</v>
       </c>
       <c r="N343" s="3" t="n">
         <v>490</v>
@@ -20280,12 +20284,702 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>M16A4:レゾナンス･ゼロ 先鋒版</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>銃器</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="n">
+        <v>1622</v>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G344" s="3" t="n">
+        <v>1841</v>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="n">
+        <v>1446</v>
+      </c>
+      <c r="J344" s="2" t="inlineStr">
+        <is>
+          <t>M16A4: Dark Matter Vanguard Edition</t>
+        </is>
+      </c>
+      <c r="K344" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="L344" s="3" t="n">
+        <v>1622</v>
+      </c>
+      <c r="M344" s="3" t="n">
+        <v>3882</v>
+      </c>
+      <c r="N344" s="3" t="n">
+        <v>3243</v>
+      </c>
+      <c r="O344" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>M16A4:レゾナンス･ゼロ 豪華版</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>銃器</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="n">
+        <v>2108</v>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G345" s="3" t="n">
+        <v>2108</v>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>M16A4: Dark Matter Enjoy Edition</t>
+        </is>
+      </c>
+      <c r="K345" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="L345" s="3" t="n">
+        <v>2108</v>
+      </c>
+      <c r="M345" s="3" t="n">
+        <v>1621555</v>
+      </c>
+      <c r="N345" s="3" t="n">
+        <v>4054</v>
+      </c>
+      <c r="O345" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>M16A4:レゾナンス･ゼロ 進化版</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>銃器</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr"/>
+      <c r="E346" s="2" t="inlineStr"/>
+      <c r="F346" s="2" t="inlineStr"/>
+      <c r="G346" s="3" t="inlineStr"/>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>直近30日間の取引データなし</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="n">
+        <v>1448</v>
+      </c>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>M16A4: Dark Matter Hum Advanced Edition</t>
+        </is>
+      </c>
+      <c r="K346" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="L346" s="3" t="inlineStr"/>
+      <c r="M346" s="3" t="inlineStr"/>
+      <c r="N346" s="3" t="n">
+        <v>4865</v>
+      </c>
+      <c r="O346" s="2" t="inlineStr"/>
+      <c r="P346" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>M16A4:レゾナンス･ゼロ 旗艦版</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>銃器</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr"/>
+      <c r="E347" s="2" t="inlineStr"/>
+      <c r="F347" s="2" t="inlineStr"/>
+      <c r="G347" s="3" t="inlineStr"/>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>直近30日間の取引データなし</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="n">
+        <v>1449</v>
+      </c>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>M16A4: Dark Matter Flagship Edition</t>
+        </is>
+      </c>
+      <c r="K347" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="L347" s="3" t="n">
+        <v>4540</v>
+      </c>
+      <c r="M347" s="3" t="n">
+        <v>6796</v>
+      </c>
+      <c r="N347" s="3" t="n">
+        <v>6486</v>
+      </c>
+      <c r="O347" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>M16A4:レゾナンス･ゼロ 豪華版Ⅰ</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>銃器</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr"/>
+      <c r="E348" s="2" t="inlineStr"/>
+      <c r="F348" s="2" t="inlineStr"/>
+      <c r="G348" s="3" t="inlineStr"/>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>直近30日間の取引データなし</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>M16A4: Dark Matter Deluxe Edition I</t>
+        </is>
+      </c>
+      <c r="K348" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="L348" s="3" t="inlineStr"/>
+      <c r="M348" s="3" t="inlineStr"/>
+      <c r="N348" s="3" t="n">
+        <v>12972</v>
+      </c>
+      <c r="O348" s="2" t="inlineStr"/>
+      <c r="P348" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>M16A4:レゾナンス･ゼロ 豪華版Ⅱ</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>銃器</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="n">
+        <v>9729</v>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G349" s="3" t="n">
+        <v>9729</v>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="n">
+        <v>1451</v>
+      </c>
+      <c r="J349" s="2" t="inlineStr">
+        <is>
+          <t>M16A4: Dark Matter Deluxe Edition II</t>
+        </is>
+      </c>
+      <c r="K349" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="L349" s="3" t="n">
+        <v>9729</v>
+      </c>
+      <c r="M349" s="3" t="n">
+        <v>19418</v>
+      </c>
+      <c r="N349" s="3" t="n">
+        <v>19459</v>
+      </c>
+      <c r="O349" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P349" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>M16A4:レゾナンス･ゼロ 豪華版Ⅲ</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>銃器</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr"/>
+      <c r="E350" s="2" t="inlineStr"/>
+      <c r="F350" s="2" t="inlineStr"/>
+      <c r="G350" s="3" t="inlineStr"/>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>直近30日間の取引データなし</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="n">
+        <v>1452</v>
+      </c>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>M16A4: Dark Matter Deluxe Edition III</t>
+        </is>
+      </c>
+      <c r="K350" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="L350" s="3" t="inlineStr"/>
+      <c r="M350" s="3" t="inlineStr"/>
+      <c r="N350" s="3" t="n">
+        <v>25945</v>
+      </c>
+      <c r="O350" s="2" t="inlineStr"/>
+      <c r="P350" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>M16A4:レゾナンス･ゼロ 周年DX Ⅰ</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>銃器</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="n">
+        <v>16216</v>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G351" s="3" t="n">
+        <v>16512</v>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="n">
+        <v>1453</v>
+      </c>
+      <c r="J351" s="2" t="inlineStr">
+        <is>
+          <t>M16A4: Dark Matter Resonance - Anniversary Supreme I</t>
+        </is>
+      </c>
+      <c r="K351" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="L351" s="3" t="n">
+        <v>16216</v>
+      </c>
+      <c r="M351" s="3" t="n">
+        <v>48543</v>
+      </c>
+      <c r="N351" s="3" t="n">
+        <v>32431</v>
+      </c>
+      <c r="O351" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="P351" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>M16A4:レゾナンス･ゼロ 周年DX Ⅱ</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>銃器</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="n">
+        <v>50484</v>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G352" s="3" t="n">
+        <v>47969</v>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="n">
+        <v>1454</v>
+      </c>
+      <c r="J352" s="2" t="inlineStr">
+        <is>
+          <t>M16A4: Dark Matter Resonance - Anniversary Supreme II</t>
+        </is>
+      </c>
+      <c r="K352" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="L352" s="3" t="n">
+        <v>53401</v>
+      </c>
+      <c r="M352" s="3" t="n">
+        <v>53401</v>
+      </c>
+      <c r="N352" s="3" t="n">
+        <v>77835</v>
+      </c>
+      <c r="O352" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P352" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>M16A4:レゾナンス･ゼロ 周年DX Ⅲ</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>銃器</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="inlineStr"/>
+      <c r="E353" s="2" t="inlineStr"/>
+      <c r="F353" s="2" t="inlineStr"/>
+      <c r="G353" s="3" t="inlineStr"/>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>直近30日間の取引データなし</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="n">
+        <v>1455</v>
+      </c>
+      <c r="J353" s="2" t="inlineStr">
+        <is>
+          <t>M16A4: Dark Matter Resonance - Anniversary Supreme III</t>
+        </is>
+      </c>
+      <c r="K353" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="L353" s="3" t="n">
+        <v>242713</v>
+      </c>
+      <c r="M353" s="3" t="n">
+        <v>388542</v>
+      </c>
+      <c r="N353" s="3" t="n">
+        <v>210802</v>
+      </c>
+      <c r="O353" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P353" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>ゼロ･ヴァンガード･スペシャルBOX</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>お宝 / 宝箱</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="n">
+        <v>9081</v>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G354" s="3" t="n">
+        <v>9081</v>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="n">
+        <v>1463</v>
+      </c>
+      <c r="J354" s="2" t="inlineStr">
+        <is>
+          <t>Stellar Core Era · Golden Gift Box</t>
+        </is>
+      </c>
+      <c r="K354" s="2" t="inlineStr">
+        <is>
+          <t>Treasure / treasure chest</t>
+        </is>
+      </c>
+      <c r="L354" s="3" t="n">
+        <v>9081</v>
+      </c>
+      <c r="M354" s="3" t="n">
+        <v>19418</v>
+      </c>
+      <c r="N354" s="3" t="n">
+        <v>18161</v>
+      </c>
+      <c r="O354" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="P354" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>ヴェスパーライン･スペシャルBOX</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>お宝 / 宝箱</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="inlineStr"/>
+      <c r="E355" s="2" t="inlineStr"/>
+      <c r="F355" s="2" t="inlineStr"/>
+      <c r="G355" s="3" t="inlineStr"/>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>直近30日間の取引データなし</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="n">
+        <v>1464</v>
+      </c>
+      <c r="J355" s="2" t="inlineStr">
+        <is>
+          <t>Stardust Echo · Golden Gift Box</t>
+        </is>
+      </c>
+      <c r="K355" s="2" t="inlineStr">
+        <is>
+          <t>Treasure / treasure chest</t>
+        </is>
+      </c>
+      <c r="L355" s="3" t="n">
+        <v>9081</v>
+      </c>
+      <c r="M355" s="3" t="n">
+        <v>22329</v>
+      </c>
+      <c r="N355" s="3" t="n">
+        <v>18161</v>
+      </c>
+      <c r="O355" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="P355" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P343"/>
+  <autoFilter ref="A1:P355"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20310,7 +21004,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>162.171846</v>
+        <v>162.155515</v>
       </c>
     </row>
     <row r="2">
@@ -20321,7 +21015,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Wed, 15 Jul 2026 00:02:32 +0000)</t>
+          <t>open.er-api.com (取得日時: Thu, 16 Jul 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -20333,7 +21027,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
